--- a/data/trans_camb/IP43-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP43-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 6,97</t>
+          <t>-13,98; 7,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,22; -16,8</t>
+          <t>-30,38; -16,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 3,18</t>
+          <t>-14,75; 3,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,7; -10,65</t>
+          <t>-23,56; -10,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 1,59</t>
+          <t>-11,6; 1,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,93; -15,63</t>
+          <t>-25,2; -15,39</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 40,52</t>
+          <t>-52,62; 39,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,69; 28,17</t>
+          <t>-68,8; 30,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 9,2</t>
+          <t>-50,09; 12,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,02; -6,91</t>
+          <t>-15,46; -7,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,21; -20,51</t>
+          <t>-27,3; -20,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -9,52</t>
+          <t>-17,62; -9,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,66; -22,06</t>
+          <t>-28,56; -22,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,01; -9,37</t>
+          <t>-15,22; -9,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -22,47</t>
+          <t>-26,88; -22,6</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,88; -33,14</t>
+          <t>-58,62; -32,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,31; -40,77</t>
+          <t>-62,33; -39,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,68; -40,43</t>
+          <t>-57,02; -40,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -5,43</t>
+          <t>-18,08; -5,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,52; -15,91</t>
+          <t>-25,81; -15,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,3; -5,31</t>
+          <t>-16,96; -4,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,09; -15,88</t>
+          <t>-25,95; -15,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -6,73</t>
+          <t>-15,07; -6,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,15; -16,91</t>
+          <t>-24,33; -17,13</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,74; -31,78</t>
+          <t>-72,75; -30,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,33; -27,75</t>
+          <t>-69,73; -29,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,3; -37,11</t>
+          <t>-66,31; -38,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -7,09</t>
+          <t>-14,03; -7,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,73; -20,51</t>
+          <t>-25,42; -20,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -8,83</t>
+          <t>-15,18; -8,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,97; -20,78</t>
+          <t>-26,03; -21,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,57; -8,89</t>
+          <t>-13,37; -8,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,17; -21,32</t>
+          <t>-24,98; -21,5</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -34,58</t>
+          <t>-56,01; -34,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,63; -40,88</t>
+          <t>-59,63; -40,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -40,76</t>
+          <t>-55,49; -40,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
